--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254701</v>
+        <v>123254299</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577702</v>
+        <v>577592</v>
       </c>
       <c r="R2" t="n">
-        <v>7064271</v>
+        <v>7064257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254299</v>
+        <v>123254701</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577592</v>
+        <v>577702</v>
       </c>
       <c r="R5" t="n">
-        <v>7064257</v>
+        <v>7064271</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,12 +1136,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254299</v>
+        <v>123254482</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577592</v>
+        <v>577637</v>
       </c>
       <c r="R2" t="n">
-        <v>7064257</v>
+        <v>7064299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254482</v>
+        <v>123254701</v>
       </c>
       <c r="B4" t="n">
         <v>56688</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577637</v>
+        <v>577702</v>
       </c>
       <c r="R4" t="n">
-        <v>7064299</v>
+        <v>7064271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254701</v>
+        <v>123254299</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577702</v>
+        <v>577592</v>
       </c>
       <c r="R5" t="n">
-        <v>7064271</v>
+        <v>7064257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,12 +1136,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254482</v>
+        <v>123254299</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577637</v>
+        <v>577592</v>
       </c>
       <c r="R2" t="n">
-        <v>7064299</v>
+        <v>7064257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123254728</v>
+        <v>123254701</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577703</v>
+        <v>577702</v>
       </c>
       <c r="R3" t="n">
-        <v>7064275</v>
+        <v>7064271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254701</v>
+        <v>123254728</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +921,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577702</v>
+        <v>577703</v>
       </c>
       <c r="R4" t="n">
-        <v>7064271</v>
+        <v>7064275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254299</v>
+        <v>123254482</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577592</v>
+        <v>577637</v>
       </c>
       <c r="R5" t="n">
-        <v>7064257</v>
+        <v>7064299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254299</v>
+        <v>123254701</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577592</v>
+        <v>577702</v>
       </c>
       <c r="R2" t="n">
-        <v>7064257</v>
+        <v>7064271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123254701</v>
+        <v>123254728</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577702</v>
+        <v>577703</v>
       </c>
       <c r="R3" t="n">
-        <v>7064271</v>
+        <v>7064275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254728</v>
+        <v>123254482</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577703</v>
+        <v>577637</v>
       </c>
       <c r="R4" t="n">
-        <v>7064275</v>
+        <v>7064299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254482</v>
+        <v>123254299</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577637</v>
+        <v>577592</v>
       </c>
       <c r="R5" t="n">
-        <v>7064299</v>
+        <v>7064257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254701</v>
+        <v>123254482</v>
       </c>
       <c r="B2" t="n">
         <v>56691</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577702</v>
+        <v>577637</v>
       </c>
       <c r="R2" t="n">
-        <v>7064271</v>
+        <v>7064299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123254728</v>
+        <v>123254299</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577703</v>
+        <v>577592</v>
       </c>
       <c r="R3" t="n">
-        <v>7064275</v>
+        <v>7064257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254482</v>
+        <v>123254701</v>
       </c>
       <c r="B4" t="n">
         <v>56691</v>
@@ -959,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577637</v>
+        <v>577702</v>
       </c>
       <c r="R4" t="n">
-        <v>7064299</v>
+        <v>7064271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254299</v>
+        <v>123254728</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1042,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1076,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577592</v>
+        <v>577703</v>
       </c>
       <c r="R5" t="n">
-        <v>7064257</v>
+        <v>7064275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123254701</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123254482</v>
+        <v>123254728</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577637</v>
+        <v>577703</v>
       </c>
       <c r="R3" t="n">
-        <v>7064299</v>
+        <v>7064275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254728</v>
+        <v>123254299</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577703</v>
+        <v>577592</v>
       </c>
       <c r="R4" t="n">
-        <v>7064275</v>
+        <v>7064257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254299</v>
+        <v>123254482</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>56697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577592</v>
+        <v>577637</v>
       </c>
       <c r="R5" t="n">
-        <v>7064257</v>
+        <v>7064299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254701</v>
+        <v>123254728</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577702</v>
+        <v>577703</v>
       </c>
       <c r="R2" t="n">
-        <v>7064271</v>
+        <v>7064275</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123254728</v>
+        <v>123254701</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577703</v>
+        <v>577702</v>
       </c>
       <c r="R3" t="n">
-        <v>7064275</v>
+        <v>7064271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +902,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -917,7 +917,7 @@
         <v>123254299</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>123254482</v>
       </c>
       <c r="B5" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254728</v>
+        <v>123254299</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577703</v>
+        <v>577592</v>
       </c>
       <c r="R2" t="n">
-        <v>7064275</v>
+        <v>7064257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123254701</v>
+        <v>123254482</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577702</v>
+        <v>577637</v>
       </c>
       <c r="R3" t="n">
-        <v>7064271</v>
+        <v>7064299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254299</v>
+        <v>123254701</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +921,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577592</v>
+        <v>577702</v>
       </c>
       <c r="R4" t="n">
-        <v>7064257</v>
+        <v>7064271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254482</v>
+        <v>123254728</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577637</v>
+        <v>577703</v>
       </c>
       <c r="R5" t="n">
-        <v>7064299</v>
+        <v>7064275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254299</v>
+        <v>123254701</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577592</v>
+        <v>577702</v>
       </c>
       <c r="R2" t="n">
-        <v>7064257</v>
+        <v>7064271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254701</v>
+        <v>123254728</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577702</v>
+        <v>577703</v>
       </c>
       <c r="R4" t="n">
-        <v>7064271</v>
+        <v>7064275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254728</v>
+        <v>123254299</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1071,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577703</v>
+        <v>577592</v>
       </c>
       <c r="R5" t="n">
-        <v>7064275</v>
+        <v>7064257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123254701</v>
+        <v>123254299</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577702</v>
+        <v>577592</v>
       </c>
       <c r="R2" t="n">
-        <v>7064271</v>
+        <v>7064257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123254482</v>
+        <v>123254728</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577637</v>
+        <v>577703</v>
       </c>
       <c r="R3" t="n">
-        <v>7064299</v>
+        <v>7064275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123254728</v>
+        <v>123254482</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577703</v>
+        <v>577637</v>
       </c>
       <c r="R4" t="n">
-        <v>7064275</v>
+        <v>7064299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123254299</v>
+        <v>123254701</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577592</v>
+        <v>577702</v>
       </c>
       <c r="R5" t="n">
-        <v>7064257</v>
+        <v>7064271</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,12 +1136,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>123254299</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -795,12 +790,7 @@
         <v>123254728</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,12 +907,7 @@
         <v>123254482</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,12 +1019,7 @@
         <v>123254701</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8077-2025 artfynd.xlsx
+++ b/artfynd/A 8077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123254299</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123254728</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123254482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,8 +1145,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123254701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>